--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-07-2025.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>£11.04</t>
+          <t>£10.98</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>£11.39</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-tb4025-25mm/</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>£12.68</t>
+          <t>£12.62</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>£13.35</t>
+          <t>£12.35</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>£16.26</t>
+          <t>£16.18</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>£16.21</t>
+          <t>£15.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>£16.54</t>
+          <t>£16.46</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>£18.45</t>
+          <t>£18.42</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>£21.18</t>
+          <t>£21.08</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>£22.21</t>
+          <t>£22.52</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>£22.88</t>
+          <t>£22.76</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>£24.3</t>
+          <t>£22.49</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>£23.21</t>
+          <t>£23.09</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>£24.48</t>
+          <t>£22.68</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>£26.46</t>
+          <t>£26.33</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>£28.96</t>
+          <t>£28.82</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>£29.9</t>
+          <t>£27.69</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>£28.26</t>
+          <t>£28.12</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>£30.95</t>
+          <t>£28.81</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>£34.66</t>
+          <t>£34.48</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>£36.86</t>
+          <t>£34.13</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>£42.27</t>
+          <t>£42.06</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>£43.26</t>
+          <t>£43.04</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>£45.51</t>
+          <t>£45.54</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>£43.05</t>
+          <t>£42.83</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>£720.42</t>
+          <t>£716.82</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>£714.4</t>
+          <t>£768.52</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>£904.42</t>
+          <t>£899.89</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>£943.2</t>
+          <t>£932.01</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>£29.43</t>
+          <t>£29.28</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>£36.92</t>
+          <t>£36.95</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>£36.29</t>
+          <t>£36.11</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>£39.41</t>
+          <t>£39.21</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>£52.35</t>
+          <t>£52.32</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>£43.97</t>
+          <t>£43.75</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>£44.65</t>
+          <t>£44.43</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>£44.53</t>
+          <t>£41.25</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>£48.23</t>
+          <t>£47.99</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>£42.56</t>
+          <t>£39.38</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>£44.24</t>
+          <t>£44.02</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>£43.78</t>
+          <t>£40.53</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>£1142.11</t>
+          <t>£1057.71</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>£1216.37</t>
+          <t>£1126.15</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>£1184.38</t>
+          <t>£1096.66</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
